--- a/data/trans_bre/P3A_R1-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P3A_R1-Edad-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que las tareas domésticas las realiza principalmente el/la entrevistado/a junto con su pareja</t>
+          <t>Hogares en los que las tareas domésticas las realiza principalmente la persona entrevistada junto con su pareja</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 3,67</t>
+          <t>-1,78; 3,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 4,92</t>
+          <t>-2,1; 4,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,17; 9,91</t>
+          <t>2,13; 9,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 7,4</t>
+          <t>-3,79; 6,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-34,25; 122,25</t>
+          <t>-29,67; 115,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-28,62; 104,16</t>
+          <t>-25,59; 97,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,84; 274,22</t>
+          <t>27,8; 267,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-43,91; 218,91</t>
+          <t>-43,41; 171,63</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,31; 0,71</t>
+          <t>-9,26; 0,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,86; 3,58</t>
+          <t>-6,25; 3,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-16,36; -5,56</t>
+          <t>-16,26; -5,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-18,12; 0,71</t>
+          <t>-17,1; 0,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-30,25; 2,86</t>
+          <t>-30,16; 2,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-21,99; 13,7</t>
+          <t>-20,65; 13,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-40,33; -15,98</t>
+          <t>-41,21; -16,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-54,13; 2,29</t>
+          <t>-54,68; 1,99</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-19,41; -10,03</t>
+          <t>-19,48; -9,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-26,86; -16,55</t>
+          <t>-26,96; -16,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-19,76; -8,48</t>
+          <t>-18,49; -8,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-19,03; -3,65</t>
+          <t>-18,78; -3,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-59,89; -36,73</t>
+          <t>-59,99; -36,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-58,66; -41,06</t>
+          <t>-59,1; -40,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-38,96; -19,06</t>
+          <t>-37,48; -18,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-41,06; -8,88</t>
+          <t>-41,18; -8,79</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-17,93; -9,28</t>
+          <t>-17,86; -9,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-25,37; -15,36</t>
+          <t>-25,1; -15,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-23,81; -13,41</t>
+          <t>-23,57; -13,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 19,71</t>
+          <t>-6,83; 18,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-75,28; -50,09</t>
+          <t>-76,83; -50,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-70,82; -51,1</t>
+          <t>-70,23; -50,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-58,0; -37,9</t>
+          <t>-58,17; -38,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-19,24; 178,16</t>
+          <t>-20,08; 164,66</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,31; -1,06</t>
+          <t>-10,18; -1,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-20,81; -9,45</t>
+          <t>-20,68; -9,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-25,98; -14,93</t>
+          <t>-26,51; -15,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-14,93; -6,4</t>
+          <t>-15,22; -6,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-58,75; -8,26</t>
+          <t>-60,97; -4,31</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-70,18; -39,73</t>
+          <t>-69,94; -42,19</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-70,35; -47,61</t>
+          <t>-70,59; -49,12</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-44,07; -23,1</t>
+          <t>-44,46; -22,25</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-18,16; -6,55</t>
+          <t>-18,12; -6,57</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-19,86; -7,97</t>
+          <t>-19,73; -8,01</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-23,83; -11,85</t>
+          <t>-23,46; -11,86</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-27,31; -12,52</t>
+          <t>-26,7; -12,72</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-65,5; -31,12</t>
+          <t>-65,13; -30,49</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-76,07; -41,88</t>
+          <t>-75,47; -42,47</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-74,11; -46,94</t>
+          <t>-74,68; -48,46</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-86,95; -48,14</t>
+          <t>-89,54; -48,62</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-17,3; -6,38</t>
+          <t>-16,97; -6,14</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-13,21; -3,91</t>
+          <t>-13,31; -3,47</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-19,44; -9,62</t>
+          <t>-19,23; -8,84</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-18,52; -10,02</t>
+          <t>-18,43; -10,06</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-85,46; -49,34</t>
+          <t>-85,47; -47,38</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-79,37; -32,78</t>
+          <t>-77,37; -32,48</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-89,68; -58,58</t>
+          <t>-88,83; -56,39</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-79,76; -59,24</t>
+          <t>-80,15; -60,17</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-10,76; -7,06</t>
+          <t>-10,78; -7,15</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-14,65; -10,56</t>
+          <t>-14,62; -10,58</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-16,06; -11,73</t>
+          <t>-16,0; -11,9</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-10,68; -1,5</t>
+          <t>-10,67; -1,12</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-49,24; -35,97</t>
+          <t>-48,63; -35,34</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-51,08; -39,8</t>
+          <t>-50,98; -40,18</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-47,73; -37,36</t>
+          <t>-47,6; -37,84</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-38,19; -9,71</t>
+          <t>-37,77; -7,67</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P3A_R1-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P3A_R1-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,78</t>
+          <t>0,85</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>13,37%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 3,71</t>
+          <t>-1,88; 3,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 4,88</t>
+          <t>-1,57; 5,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,13; 9,76</t>
+          <t>2,33; 9,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 6,53</t>
+          <t>-4,76; 5,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-29,67; 115,52</t>
+          <t>-32,66; 118,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-25,59; 97,5</t>
+          <t>-21,96; 109,86</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,8; 267,1</t>
+          <t>34,39; 278,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-43,41; 171,63</t>
+          <t>-49,56; 151,28</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-6,57</t>
+          <t>-2,63</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-22,78%</t>
+          <t>-9,68%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,26; 0,71</t>
+          <t>-9,13; 0,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 3,62</t>
+          <t>-6,39; 3,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-16,26; -5,73</t>
+          <t>-16,28; -5,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-17,1; 0,83</t>
+          <t>-9,09; 3,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-30,16; 2,89</t>
+          <t>-30,53; 2,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-20,65; 13,93</t>
+          <t>-20,7; 14,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-41,21; -16,71</t>
+          <t>-41,49; -16,31</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-54,68; 1,99</t>
+          <t>-28,98; 17,81</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-9,7</t>
+          <t>-7,21</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-21,97%</t>
+          <t>-16,69%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-19,48; -9,94</t>
+          <t>-19,0; -10,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-26,96; -16,86</t>
+          <t>-27,2; -17,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-18,49; -8,39</t>
+          <t>-18,6; -7,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-18,78; -3,48</t>
+          <t>-12,58; -1,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-59,99; -36,71</t>
+          <t>-59,01; -37,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-59,1; -40,87</t>
+          <t>-58,63; -41,36</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-37,48; -18,49</t>
+          <t>-38,03; -16,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-41,18; -8,79</t>
+          <t>-27,39; -4,1</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,15</t>
+          <t>-4,98</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>-14,62%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-17,86; -9,08</t>
+          <t>-17,82; -9,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-25,1; -15,05</t>
+          <t>-25,31; -15,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-23,57; -13,57</t>
+          <t>-23,82; -13,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,83; 18,82</t>
+          <t>-9,51; -0,57</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-76,83; -50,12</t>
+          <t>-76,04; -49,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-70,23; -50,16</t>
+          <t>-70,12; -50,13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-58,17; -38,83</t>
+          <t>-59,12; -38,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-20,08; 164,66</t>
+          <t>-25,86; -1,72</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-10,76</t>
+          <t>-10,65</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-34,09%</t>
+          <t>-33,7%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,18; -1,0</t>
+          <t>-9,97; -1,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-20,68; -9,96</t>
+          <t>-20,62; -9,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-26,51; -15,15</t>
+          <t>-25,53; -14,34</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-15,22; -6,54</t>
+          <t>-15,37; -6,27</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-60,97; -4,31</t>
+          <t>-62,2; -11,62</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-69,94; -42,19</t>
+          <t>-69,6; -41,94</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-70,59; -49,12</t>
+          <t>-70,82; -49,05</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-44,46; -22,25</t>
+          <t>-44,35; -21,11</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-18,69</t>
+          <t>-14,45</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-68,48%</t>
+          <t>-52,92%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-18,12; -6,57</t>
+          <t>-17,91; -6,01</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-19,73; -8,01</t>
+          <t>-19,59; -8,16</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-23,46; -11,86</t>
+          <t>-23,89; -12,21</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-26,7; -12,72</t>
+          <t>-18,85; -10,4</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-65,13; -30,49</t>
+          <t>-66,0; -30,55</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-75,47; -42,47</t>
+          <t>-75,18; -43,05</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-74,68; -48,46</t>
+          <t>-75,06; -49,22</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-89,54; -48,62</t>
+          <t>-61,77; -41,45</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-14,17</t>
+          <t>-13,74</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-71,7%</t>
+          <t>-71,42%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-16,97; -6,14</t>
+          <t>-17,3; -6,39</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-13,31; -3,47</t>
+          <t>-13,85; -3,42</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-19,23; -8,84</t>
+          <t>-18,83; -8,9</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-18,43; -10,06</t>
+          <t>-17,54; -9,14</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-85,47; -47,38</t>
+          <t>-85,63; -46,08</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-77,37; -32,48</t>
+          <t>-78,71; -29,11</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-88,83; -56,39</t>
+          <t>-88,84; -57,62</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-80,15; -60,17</t>
+          <t>-79,8; -58,34</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-7,14</t>
+          <t>-7,7</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-26,48%</t>
+          <t>-26,51%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-10,78; -7,15</t>
+          <t>-10,64; -7,02</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-14,62; -10,58</t>
+          <t>-14,51; -10,52</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-16,0; -11,9</t>
+          <t>-15,71; -11,62</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-10,67; -1,12</t>
+          <t>-9,73; -5,59</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-48,63; -35,34</t>
+          <t>-48,97; -34,99</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-50,98; -40,18</t>
+          <t>-50,67; -39,92</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-47,6; -37,84</t>
+          <t>-47,31; -37,07</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-37,77; -7,67</t>
+          <t>-31,93; -20,2</t>
         </is>
       </c>
     </row>
